--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <color rgb="00006100"/>
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,42 +433,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Awarded Value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Buyer Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Estimated Value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Winner Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Awarded Currency</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Estimated Currency</t>
         </is>
@@ -497,7 +485,7 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>3600000</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -505,7 +493,7 @@
           <t>Myndigheten för Tillgängliga Medier</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>2000000</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -525,76 +513,76 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>84600000</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Region Sörmland och Region Västmanland</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>16000000</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Exsitec AB, Exsitec AB</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Liseberg AB</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>16000000</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Exsitec AB</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
@@ -611,7 +599,7 @@
           <t>2025-04-15</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>18000000</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -619,7 +607,7 @@
           <t>Linköpings kommun</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Drake Analytics AB</t>
@@ -633,38 +621,38 @@
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2025-03-05</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>10196616</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Roslagsbostäder AB</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>2500000</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Exsitec AB</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
@@ -681,7 +669,7 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>4500000</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -689,7 +677,7 @@
           <t>Nacka kommun</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>4500000</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -719,7 +707,7 @@
           <t>2025-01-22</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="n">
         <v>11402695</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -727,7 +715,7 @@
           <t>Region Kronoberg</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>15000000</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -757,7 +745,7 @@
           <t>2025-01-21</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="1" t="n">
         <v>22000000</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -765,7 +753,7 @@
           <t>Kraftringen Energi AB (publ)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>40000000</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -795,7 +783,7 @@
           <t>2025-01-15</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="1" t="n">
         <v>12000000</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -803,7 +791,7 @@
           <t>E-hälsomyndigheten</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Artvise AB</t>
@@ -827,7 +815,7 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="1" t="n">
         <v>1500000</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -835,7 +823,7 @@
           <t>Linköpings universitet</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
@@ -855,7 +843,7 @@
           <t>2023-04-18</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="1" t="n">
         <v>5000000</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -863,7 +851,7 @@
           <t>Nacka kommun</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
@@ -883,7 +871,7 @@
           <t>2022-03-04</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="1" t="n">
         <v>8750000</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -891,7 +879,7 @@
           <t>ARBETSGIVARVERKET</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
@@ -911,7 +899,7 @@
           <t>2021-05-14</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="1" t="n">
         <v>110000000</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -919,7 +907,7 @@
           <t>Region Östergötland</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exsitec AB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQL Pharma AB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQL Pharma AB Detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <color rgb="00006100"/>
@@ -37,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +50,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,42 +447,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Awarded Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Buyer Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Estimated Value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Winner Name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Awarded Currency</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Estimated Currency</t>
         </is>
@@ -482,111 +496,81 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>3600000</v>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>110000000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Myndigheten för Tillgängliga Medier</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Capgemini Sverige AB</t>
-        </is>
-      </c>
+          <t>Region Östergötland</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>84600000</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Region Sörmland och Region Västmanland</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Exsitec AB, Exsitec AB</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-03-04</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>8750000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ARBETSGIVARVERKET</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Liseberg AB</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Exsitec AB</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Nacka kommun</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,23 +580,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>18000000</v>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1500000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Linköpings kommun</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Drake Analytics AB</t>
-        </is>
-      </c>
+          <t>Linköpings universitet</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>SEK</t>
@@ -621,42 +601,36 @@
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>10196616</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Roslagsbostäder AB</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Exsitec AB</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E-hälsomyndigheten</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Artvise AB</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -666,23 +640,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>4500000</v>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>22000000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nacka kommun</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>4500000</v>
+          <t>Kraftringen Energi AB (publ)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>40000000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xenit AB</t>
+          <t>Absfront AB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,7 +681,7 @@
           <t>2025-01-22</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>11402695</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -715,7 +689,7 @@
           <t>Region Kronoberg</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>15000000</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -742,35 +716,509 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>22000000</v>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4500000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kraftringen Energi AB (publ)</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
+          <t>Nacka kommun</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Xenit AB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>10196616</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Roslagsbostäder AB</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Exsitec AB</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Linköpings kommun</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Drake Analytics AB</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Liseberg AB</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Exsitec AB</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>84600000</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Region Sörmland och Region Västmanland</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Exsitec AB, Exsitec AB</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Myndigheten för Tillgängliga Medier</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Capgemini Sverige AB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Publication Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Awarded Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buyer Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Winner Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Awarded Currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2021-11-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Region Halland</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>40000000</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Absfront AB</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Region Halland</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>64100000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2022-12-13</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -780,23 +1228,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>12000000</v>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>740437852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>E-hälsomyndigheten</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Artvise AB</t>
-        </is>
-      </c>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>SEK</t>
@@ -812,18 +1256,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1500000</v>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2000000000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Linköpings universitet</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr"/>
+          <t>Region Stockholm</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
@@ -840,18 +1284,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>5000000</v>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>85550000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nacka kommun</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr"/>
+          <t>Region Jönköpings Län</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
@@ -868,22 +1312,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2022-03-04</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>8750000</v>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2820000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ARBETSGIVARVERKET</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr"/>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -896,25 +1340,7192 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>110000000</v>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>8520000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Region Östergötland</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr"/>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3710000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>33500000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>67900000</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>167000000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2023-12-12</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>5515497000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, CSL Behring Aktiebolag, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, medac, Nordic Drugs Aktiebolag, Norgine A/S, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, CSL Behring Aktiebolag, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, medac, Nordic Drugs Aktiebolag, Norgine A/S, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, Nordic Drugs Aktiebolag, Norgine A/S, Pfizer Aktiebolag, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, CSL Behring Aktiebolag, Fresenius Kabi AB, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Roche Aktiebolag, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Baxter Medical AB, betapharm Arzneimittel GmbH, FrostPharma AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, medac, Roche Aktiebolag, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, betapharm Arzneimittel GmbH, Fresenius Kabi AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Sandoz A/S, Sun Pharmaceutical Germany GmbH</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>35886000</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Aguettant Nordic ApS, Macure Pharma ApS, Unimedic Pharma AB, Aguettant Nordic ApS, Abboxia AB, Øresund Pharma ApS, Abacus Medicine A/S, Orifarm A/S, Zentiva Denmark ApS, Accord Healthcare AB, 2care4 ApS, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>12855000</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>34600003</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Medical Valley Invest AB, Orifarm Generics A/S, Sandoz A/S, Haleon Denmark ApS, Medical Valley Invest AB, Krka Sverige AB, Sandoz A/S, Orifarm Generics A/S, Haleon Denmark ApS, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Orifarm Generics A/S, Teva Denmark A/S, Orifarm Generics A/S, Teva Denmark A/S, Orifarm Generics A/S, Teva Denmark A/S, Macure Pharma ApS, Macure Pharma ApS, Macure Pharma ApS, Macure Pharma ApS, EQL Pharma AB, EQL Pharma AB, Orifarm Generics A/S</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>9080000</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Orifarm Generics A/S, Grünenthal Denmark ApS, Teva Denmark A/S, Medical Valley Invest AB, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>4927000</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>20899997</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, Haleon Denmark ApS, Haleon Denmark ApS, EQL Pharma AB, Abcur AB, Hameln Pharma ApS, Øresund Pharma ApS, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>68731000</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>96100002</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Jazz Pharmaceuticals Denmark ApS, Sandoz A/S, Medical Valley Invest AB, Sandoz A/S, Sandoz A/S, Chiesi Pharma AB, 2care4 ApS, 2care4 ApS, Haleon Denmark ApS, Haleon Denmark ApS, Haleon Denmark ApS, McNeil Denmark ApS, McNeil Denmark ApS, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>56597000</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>129999998</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Panpharma Nordic AS, Panpharma Nordic AS, Sandoz A/S, EQL Pharma AB, Panpharma Nordic AS, Stragen Nordic A/S, Navamedic AB, Macure Pharma ApS, Stragen Nordic A/S, Navamedic AB, Macure Pharma ApS, XGX Pharma ApS, 2care4 ApS, Macure Pharma ApS, Fresenius Kabi, Navamedic AB, Pfizer ApS, Sun Pharmaceuticals Germany GmbH, MSD Danmark ApS, Orifarm A/S, 2care4 ApS, MSD Danmark ApS, Hameln Pharma ApS, Orifarm Generics A/S, Orifarm A/S, FrostPharma AB, Accord Healthcare AB, Hameln Pharma ApS, MSD Danmark ApS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>35346000</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>80099999</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Sandoz A/S, 2care4 ApS, Sandoz A/S, 2care4 ApS, 2care4 ApS, Sandoz A/S, Orion Pharma A/S, Karo Healthcare AB, Orion Pharma A/S, Orion Pharma A/S, Karo Healthcare AB, EQL Pharma AB, Sandoz A/S, 2care4 ApS, 2care4 ApS, Sandoz A/S, 2care4 ApS, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orifarm Generics A/S, Krka Sverige AB, Sandoz A/S, 2care4 ApS, Krka Sverige AB, Krka Sverige AB, Sandoz A/S, 2care4 ApS, Accord Healthcare AB, 2care4 ApS, Teva Denmark A/S, STADA Nordic ApS, Krka Sverige AB, Teva Denmark A/S, STADA Nordic ApS, Krka Sverige AB, Krka Sverige AB, Pfizer ApS, Orifarm Generics A/S, Pfizer ApS, STADA Nordic ApS, STADA Nordic ApS, Krka Sverige AB, STADA Nordic ApS, Krka Sverige AB, Orion Pharma A/S, Krka Sverige AB, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Finnish Institute for Health and Welfare</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, Orion Oyj, Orion Oyj, EQL Pharma AB, Orion Oyj</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Vankiterveydenhuollon yksikkö, Niuvanniemen sairaala, Vanhan Vaasan sairaala</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Ailon Pharma Oy, Aguettant Nordic ApS, Avansor Pharma Oy, Bausch Lomb Nordic, Bayer Oy, Berner Oy, B. Braun Medical Oy, Camurus AB, DNE PHARMA AS, EQL Pharma AB, Essential Pharma Limited, Exeltis Sverige AB, filial i Finland, Fresenius Kabi Ab, FrostPharma AB, Gedeon Richter Nordics Ab, Grindeks Kalceks Suomi Oy, Haleon Finland Oy, Indivior Europe Limited, Krka Finland Oy, Mediq Suomi Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy Eli Lilly Finland Ab, Oy Verman Ab, Pierrel S.p.A., Teva Finland Oy, Viatris Oy, Ailon Pharma Oy, Avansor Pharma Oy, Bausch Lomb Nordic, Bayer Oy, CNX Therapeutics Ltd., DNE PHARMA AS, Essential Pharma Limited, Grindeks Kalceks Suomi Oy, Haleon Finland Oy, Indivior Europe Limited, Krka Finland Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy H. Lundbeck Ab, Oy Verman Ab, TD Pharma B.V., Teva Finland Oy, Viatris Oy</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>233084078</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1920000000</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Accord Healthcare AB, betapharm Arzneimittel GmbH, CAMPUS Pharma AB, EQL Pharma AB, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Medical Valley Invest AB, Orifarm Generics AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, betapharm Arzneimittel GmbH, CAMPUS Pharma AB, EQL Pharma AB, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Medical Valley Invest AB, Orifarm Generics AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, betapharm Arzneimittel GmbH, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, Sandoz A/S, Accord Healthcare AB, Fresenius Kabi AB, Macure Pharma, Medical Valley Invest AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, CAMPUS Pharma AB</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>4128000000</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>G.L. Pharma Nordic Aktiebolag, Amgen Aktiebolag, Novartis Sverige Aktiebolag, Galenica AB, Mölnlycke Health Care AB, Evolan Pharma AB, AstraZeneca AB, dne pharma as, Sandoz A/S, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Pharmacosmos A/S, Norgine A/S, Octapharma Nordic AB, Aspen Pharma Ireland Limited, Fresenius Kabi AB, Scandinavian Biopharma Distribution AB, Unimedic Pharma AB, B.Braun Medical AB, Bracco Imaging Scandinavia AB, Baxter Medical AB, hameln pharma AB, Viatris AB, Pfizer Aktiebolag, Orifarm AB, CSL Behring Aktiebolag, Orifarm Generics AB, Biogen Sweden AB, Abcur AB, FrostPharma AB, Teva Sweden Aktiebolag, Roche Aktiebolag, Aguettant Nordic ApS, Grifols Nordic AB, Vifor Pharma Nordiska AB, Recordati AB, Accord Healthcare AB, CAMPUS Pharma AB, Grindeks Kalceks Sverige AB, Macure Pharma, Takeda Pharma AB, Tillotts Pharma AB, Bausch &amp; Lomb Nordic AB, Sanofi AB, Bluefish Pharmaceuticals AB (publ), Abboxia AB, Bayer Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Finnish Institute for Health and Welfare</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Grindeks Kalceks Suomi Oy, Grindeks Kalceks Suomi Oy, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>3256789</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>11765767</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>EQL Pharma AB, Navamedic AB, FrostPharma AB</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>33696648</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>225775646</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, STADA Nordic ApS, EQL Pharma AB, Fresenius Kabi, Navamedic AB, Navamedic AB, Navamedic AB, Fresenius Kabi, B. Braun Medical AS, B. Braun Medical A/S, B. Braun Medical AS, B. Braun Medical A/S, B. Braun Medical AS, B. Braun Medical A/S, Fresenius Kabi, Navamedic AB, Hameln Pharma ApS, Orion Pharma A/S</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>513457728</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Region Blekinge</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Amgen Aktiebolag, Orifarm AB, Baxter Medical Aktiebolag, Roche Aktiebolag, Orifarm Generics AB, Grindeks Kalceks Sverige AB, Sandoz A/S, STADA Nordic ApS, Biosimilar Collaborations Ireland Limited, CAMPUS Pharma AB, betapharm Arzneimittel GmbH, Accord Healthcare AB, Glenmark Pharmaceuticals Nordic AB, Fresenius Kabi AB</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>115014000</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>370000003</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grindeks Kalceks Danmark ApS, Grindeks Kalceks Danmark ApS, 2care4 Generics ApS, G.L. Pharma Nordic Aktiebolag, STADA Nordic ApS, STADA Nordic ApS, Orifarm Generics A/S, Sandoz A/S, Grindeks Kalceks Danmark ApS, Swedish Orphan Biovitrum AB, STADA Nordic ApS, Recordati AB, McNeil Denmark ApS, Vifor Pharma Nordiska AB, STADA Nordic ApS, Vifor Pharma Nordiska AB, Orifarm Generics A/S, Viatris ApS, Abacus Medicine A/S, Abcur AB, BioMarin International Limited, Immedica Pharma AB, Amicus Therapeutics Europe Limited, Nordic Prime ApS, Takeda Pharma A/S, Takeda Pharma A/S</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>41562000</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Teva Denmark A/S, STADA Nordic ApS, STADA Nordic ApS, Krka Sverige AB, Teva Denmark A/S, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Sandoz A/S, Sandoz A/S, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Krka Sverige AB, Øresund Pharma ApS, Krka Sverige AB, Krka Sverige AB, Øresund Pharma ApS, Krka Sverige AB, Abacus Medicine A/S, Orifarm A/S, EQL Pharma AB, STADA Nordic ApS, EQL Pharma AB, STADA Nordic ApS, EQL Pharma AB, STADA Nordic ApS, Orifarm Generics A/S, McNeil Denmark ApS, Boehringer Ingelheim Danmark A/S, Boehringer Ingelheim Danmark A/S, Strides Nordic ApS, Strides Nordic ApS, 2care4 ApS, Strides Nordic ApS, Paranova Danmark A/S, Abacus Medicine A/S, Karo Healthcare AB, Orifarm Generics A/S, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>5579000</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>20900000</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, EQL Pharma AB, Orifarm Generics A/S, Recordati AB, Krka Sverige AB, Sandoz A/S, Recordati AB, Viatris ApS, Krka Sverige AB, Recordati AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>43084000</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>91400000</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Krka Sverige AB, Sandoz A/S, STADA Nordic ApS, Sanofi A/S, Orifarm Generics A/S, Teva Denmark A/S, Sandoz A/S, Teva Denmark A/S, Orifarm Generics A/S, 2care4 Generics ApS, Viatris ApS, 2care4 ApS, Zentiva Denmark ApS, Orifarm A/S, Zentiva Denmark ApS, Krka Sverige AB, Zentiva Denmark ApS, Orifarm Generics A/S, Krka Sverige AB, Zentiva Denmark ApS, Orifarm Generics A/S, EQL Pharma AB, Orifarm Generics A/S, Teva Denmark A/S, EQL Pharma AB, Abacus Medicine A/S, Takeda Pharma A/S, Takeda Pharma A/S, Abacus Medicine A/S, Strides Nordic ApS, Omet Pharma AB, Orifarm Generics A/S, Strides Nordic ApS, Omet Pharma AB, STADA Nordic ApS, STADA Nordic ApS, STADA Nordic ApS, Sandoz A/S, Orifarm Generics A/S, Teva Denmark A/S, Sandoz A/S, Orifarm Generics A/S, Teva Denmark A/S</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>32792000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>LEO Pharma A/S, Mundipharma A/S, Pharmanovia A/S, Pharmanovia A/S, Øresund Pharma ApS, Orifarm Generics A/S, Paranova Danmark A/S, 2care4 ApS, Abacus Medicine A/S, Abacus Medicine A/S, Orifarm A/S, CampusPharma AB, SERB SAS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>6020000</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>12200001</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>2care4 Generics ApS, Haleon Denmark ApS, Haleon Denmark ApS, Haleon Denmark ApS, Teva Denmark A/S, EQL Pharma AB, EQL Pharma AB, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>1860000</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>5040002</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Paranova Danmark A/S, Orifarm A/S, 2care4 Generics ApS, EQL Pharma AB, 2care4 Generics ApS, Viatris ApS</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>8465000</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>33399999</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Viatris ApS, EQL Pharma AB, Orifarm Generics A/S, Viatris ApS, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orion Pharma A/S, Orifarm Generics A/S, 2care4 ApS, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Teva Denmark A/S, Pfizer ApS, Krka Sverige AB, Sandoz A/S, STADA Nordic ApS, Krka Sverige AB, Orifarm A/S, Sandoz A/S, Paranova Danmark A/S, 2care4 ApS, Orifarm A/S, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>38466000</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>178000002</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Panpharma Nordic AS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Panpharma Nordic AS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Panpharma Nordic AS, EQL Pharma AB, Sandoz A/S, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Navamedic AB, Navamedic AB, Panpharma Nordic AS, Abcur AB, Macure Pharma ApS, Grindeks Kalceks Danmark ApS, Hameln Pharma ApS, Pfizer ApS, Abcur AB, Panpharma Nordic AS, Sandoz A/S, Sandoz A/S, Macure Pharma ApS, Orifarm A/S, 2care4 ApS, Orifarm A/S, 2care4 ApS, Abacus Medicine A/S</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-15Z</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2024-03-11Z</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Region Jönköpings Län</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-12Z</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-15Z</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>268138000</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>447642000</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2024-07-17Z</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Zentiva Denmark ApS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>10167000</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>37700001</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, Orifarm Generics A/S, Grindeks Kalceks Danmark ApS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Unimedic Pharma AB, Orifarm Generics A/S, Abcur AB</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB, Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>13690000</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>MSD Danmark ApS, EQL Pharma AB, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, 2care4 ApS, Abcur AB, Abacus Medicine A/S, Orifarm A/S, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Region Kalmar Län</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Orifarm Generics AB, B Braun Medical AB, SUN Pharmaceuticals GmbH, Baxter Medical AB, Aspen Pharma Ireland Limited, Grindeks Kalceks Sverige AB, AGUETTANT NORDIC ApS, EQL Pharma AB, Camurus AB, Viatris AB, Fresenius Kabi, Haleon Sweden AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>publication_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>buyer_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lot_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lot_title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tender_value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fa_max_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fa_max_currency</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>proc_estimated_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>proc_estimated_currency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>total_awarded_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>total_awarded_currency</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>total_lots</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>eql_lots_won</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>duration_years</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>num_tenders_on_lot</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>contract_title</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>notice_type</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>notice_title</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>publication_number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-15Z</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Generell del</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>134000000</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel 2024</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>96830-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-15Z</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Uteslutningsgrunder</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="4" t="n">
+        <v>134000000</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel 2024</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>96830-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-15Z</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0003</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Kravspecifikation</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="4" t="n">
+        <v>134000000</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel 2024</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>96830-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-11Z</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Region Jönköpings Län</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>GENERELL DEL</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2028-02-28</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel - Allmänna sortimentet 2024 (Sydöstra-J)</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>145984-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-11Z</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Region Jönköpings Län</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>GENERELL DEL (1)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>2028-02-28</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel - Allmänna sortimentet 2024 (Sydöstra-J)</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>145984-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-12Z</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2. Lääkevalmisteet ja niihin rinnastettavat valmisteet sopimuskaudelle 1.4.2024-31.3.2027 (kolme vuotta)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="4" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Finland – Pharmaceutical products – Lääkevalmisteet sekä niihin rinnastettavat valmisteet Itä-Suomen yhteistyöalueelle</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>218278-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Mallar</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="4" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Medical equipments, pharmaceuticals and personal care products – Läkemedel på rekvisition 2024, SLL450</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>243036-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Anbudsinfordran</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="4" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Medical equipments, pharmaceuticals and personal care products – Läkemedel på rekvisition 2024, SLL450</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>243036-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-15Z</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Kravspecifikation</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="4" t="n">
+        <v>223821000</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>268138000</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Infektionsläkemedel 2024</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>285836-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-15Z</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Administrativa föreskrifter</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="4" t="n">
+        <v>223821000</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>268138000</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Infektionsläkemedel 2024</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>285836-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-17Z</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 1</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1160.a</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>428954-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0009</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>G: Utvärderingskriterium för delområde 23, 24</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0008</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>F: Utvärderingskriterium för delområde 22</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0007</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>E: Utvärderingskriterium för delområde 19, 21</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0005</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>C: Utvärderingskriterium för delområde 15-17, 20</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0006</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>D: Utvärderingskriterium för delområde 18</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0003</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>A. Utvärderingskriterium för delområde 1-5, 8-12, 14, 31-46, 48-50</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Kravspecifikation</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Administrativa föreskrifter - Över tröskelvärde</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0004</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>B: Utvärderingskriterium för delområde 6-7, 13, 25-30, 47</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="4" t="n">
+        <v>612833000</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2024 del 1</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>479281-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0009</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 9</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>9318547</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>101036383</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1200.a</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>648845-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0049</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 49</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>157000</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>302396</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>27640446</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1390.b</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>650790-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0050</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 50</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>244000</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>716380</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>27640446</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1390.b</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>650790-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 1</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>9080000</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>9080000</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>9080000</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1207.b</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>651785-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0019</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 19</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>340000</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>34053</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>20900000</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>17702414</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1302.a</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>659975-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0026</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 26</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>3430000</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>4189403</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>96100000</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>83949231</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1304.a</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>660750-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0003</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 3</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>7256018</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>129999998</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 2.1310.b</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>671719-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0008</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 8</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2320000</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>2097919</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>80100000</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>74708177</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2025 1.1391.b</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>672553-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Finnish Institute for Health and Welfare</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0004</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>LOT 4: Clindamycin 300 mg (tablet/capsule, oral, ATC J01FF01)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>Finland – General anti-infectives for systemic use and vaccines – Antibacterial and antimycobacterial products for systemic use</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>70698-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Vankiterveydenhuollon yksikkö, Niuvanniemen sairaala, Vanhan Vaasan sairaala</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Rivituotteet</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>Finland – Medical equipments, pharmaceuticals and personal care products – Jälki-ilmoitus. Lääkevalmisteiden ja niihin rinnastettavien tuotteiden hankintaa koskeva tarjouspyyntö hankintakaudelle 2025-2026</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>153986-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0006</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>D. Utvärderingskriterium för delområde 8-10, 13-14, 17-18, 21-24, 27, 29</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="4" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>100350964</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel onkologi 2025</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>186750-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0007</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>E. Utvärderingskriterium för delområde 30</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="4" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>100350964</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel onkologi 2025</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>186750-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0005</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>C. Utvärderingskriterium för delområde 15-16, 19, 25-26</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="4" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>100350964</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel onkologi 2025</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>186750-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Kravspec Läkemedel</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="4" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>100350964</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel onkologi 2025</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>186750-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Administrativa föreskrifter</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="4" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>100350964</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel onkologi 2025</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>186750-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0003</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>A. Utvärderingskriterium för delområde 1, 4, 28, 31-32, 34-38</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="4" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>100350964</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel onkologi 2025</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>186750-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0000</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Läkemedel på rekvisition 2025 SLL450</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="4" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>332000000</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel på rekvisition 2025 SLL450</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>219864-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Finnish Institute for Health and Welfare</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0004</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>LOT 4: Glycopyrrhonium/neostigmin 0,5/2,5 mg/ml (1 ml per vial/ampoule i.v. ATC N07AA51)</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>Finland – Medicinal products for the nervous system – Analgesics and anesthetics for systemic use</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>260803-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Lot No. 1</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>11765767</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>375509-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Lot No. 1</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>225775606</v>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>227000000</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>376656-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Lot No. 2</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>225775606</v>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>227000000</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>376656-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0003</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Lot No. 3</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>12777840</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>225775606</v>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>227000000</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>376656-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0004</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Lot No. 4</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>225775606</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>227000000</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>376656-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Region Blekinge</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Läkemedel Cytostatika 2025</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>24450368</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="4" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel Cytostatika 2025</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>649606-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0012</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 12</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>5844466</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>370000000</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>245033539</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.700.a</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>683774-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0021</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 21</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>6546929</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>66631361</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>692426-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0012</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 12</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>5638177</v>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>66631361</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>692426-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0010</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 10</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>1118087</v>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>66631361</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>692426-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0011</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 11</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>557000</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>2328758</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>66631361</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>692426-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0006</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 6</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>447000</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>525617</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>20900000</v>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>13286794</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>710534-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0019</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 19</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>4174341</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>91400000</v>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>88050546</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>712539-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0021</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 21</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>6724462</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>91400000</v>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>88050546</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>712539-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0006</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>12568724</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>368505024</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.1203.a</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>719210-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0021</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 21</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>670000</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>846850</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>7867813</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.603.a</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>720704-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0023</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 23</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>137000</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>273738</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>7867813</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.603.a</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>720704-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0005</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 5</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>301000</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>991306</v>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>5040000</v>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>4100779</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1303.b</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>726110-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 2</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>2690000</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>6329096</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>33400000</v>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>23945273</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1390.b</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>726119-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0003</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 3</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>8124758</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>178000000</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>161990275</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1302.b</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>726933-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0007</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 7</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>2686417</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>37700000</v>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>34240300</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.12.a</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>819443-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Administrativa föreskrifter - Över tröskelvärde</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2025 del 2</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>833026-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Kravspec Läkemedel (2)</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="4" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S62" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2025 del 2</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>833026-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 1</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>5080417</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1306.b</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>53764-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Region Kalmar Län</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Rekvisitionsläkemedel - ATC-kod N 2026</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>2030-02-28</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel - ATC-kod N 2026 (Sydöstra-K)</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>171806-2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2827,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2853,6 +2853,8 @@
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="60" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2969,6 +2971,16 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>publication_number</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>is_framework</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>winners_on_lot</t>
         </is>
       </c>
     </row>
@@ -3056,6 +3068,14 @@
           <t>96830-2024</t>
         </is>
       </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3141,6 +3161,14 @@
           <t>96830-2024</t>
         </is>
       </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3226,6 +3254,14 @@
           <t>96830-2024</t>
         </is>
       </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3311,6 +3347,14 @@
           <t>145984-2024</t>
         </is>
       </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3395,6 +3439,14 @@
         <is>
           <t>145984-2024</t>
         </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -3465,6 +3517,14 @@
           <t>218278-2024</t>
         </is>
       </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3550,6 +3610,14 @@
           <t>243036-2024</t>
         </is>
       </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3635,6 +3703,14 @@
           <t>243036-2024</t>
         </is>
       </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3710,6 +3786,14 @@
           <t>285836-2024</t>
         </is>
       </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3785,6 +3869,14 @@
           <t>285836-2024</t>
         </is>
       </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3881,6 +3973,14 @@
         <is>
           <t>428954-2024</t>
         </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3957,6 +4057,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4032,6 +4140,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4107,6 +4223,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -4182,6 +4306,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -4257,6 +4389,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -4332,6 +4472,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4407,6 +4555,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4482,6 +4638,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4557,6 +4721,14 @@
           <t>479281-2024</t>
         </is>
       </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4654,6 +4826,14 @@
           <t>648845-2024</t>
         </is>
       </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4751,6 +4931,14 @@
           <t>650790-2024</t>
         </is>
       </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4848,6 +5036,14 @@
           <t>650790-2024</t>
         </is>
       </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4945,6 +5141,14 @@
           <t>651785-2024</t>
         </is>
       </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5042,6 +5246,14 @@
           <t>659975-2024</t>
         </is>
       </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5139,6 +5351,14 @@
           <t>660750-2024</t>
         </is>
       </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5236,6 +5456,14 @@
           <t>671719-2024</t>
         </is>
       </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5332,6 +5560,14 @@
         <is>
           <t>672553-2024</t>
         </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -5408,6 +5644,14 @@
           <t>70698-2025</t>
         </is>
       </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -5488,6 +5732,14 @@
         <is>
           <t>153986-2025</t>
         </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="32">
@@ -5574,6 +5826,14 @@
           <t>186750-2025</t>
         </is>
       </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -5659,6 +5919,14 @@
           <t>186750-2025</t>
         </is>
       </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -5744,6 +6012,14 @@
           <t>186750-2025</t>
         </is>
       </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -5829,6 +6105,14 @@
           <t>186750-2025</t>
         </is>
       </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -5914,6 +6198,14 @@
           <t>186750-2025</t>
         </is>
       </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -5999,6 +6291,14 @@
           <t>186750-2025</t>
         </is>
       </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -6083,6 +6383,14 @@
         <is>
           <t>219864-2025</t>
         </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="39">
@@ -6153,6 +6461,14 @@
           <t>260803-2025</t>
         </is>
       </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -6249,6 +6565,14 @@
         <is>
           <t>375509-2025</t>
         </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -6341,6 +6665,14 @@
           <t>376656-2025</t>
         </is>
       </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -6432,6 +6764,14 @@
           <t>376656-2025</t>
         </is>
       </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -6528,6 +6868,14 @@
         <is>
           <t>376656-2025</t>
         </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -6619,6 +6967,14 @@
         <is>
           <t>376656-2025</t>
         </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -6701,6 +7057,14 @@
           <t>649606-2025</t>
         </is>
       </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -6798,6 +7162,14 @@
           <t>683774-2025</t>
         </is>
       </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -6895,6 +7267,14 @@
           <t>692426-2025</t>
         </is>
       </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -6992,6 +7372,14 @@
           <t>692426-2025</t>
         </is>
       </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -7089,6 +7477,14 @@
           <t>692426-2025</t>
         </is>
       </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -7186,6 +7582,14 @@
           <t>692426-2025</t>
         </is>
       </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -7283,6 +7687,14 @@
           <t>710534-2025</t>
         </is>
       </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -7380,6 +7792,14 @@
           <t>712539-2025</t>
         </is>
       </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -7477,6 +7897,14 @@
           <t>712539-2025</t>
         </is>
       </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -7574,6 +8002,14 @@
           <t>719210-2025</t>
         </is>
       </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -7671,6 +8107,14 @@
           <t>720704-2025</t>
         </is>
       </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -7768,6 +8212,14 @@
           <t>720704-2025</t>
         </is>
       </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -7865,6 +8317,14 @@
           <t>726110-2025</t>
         </is>
       </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -7962,6 +8422,14 @@
           <t>726119-2025</t>
         </is>
       </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -8059,6 +8527,14 @@
           <t>726933-2025</t>
         </is>
       </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -8155,6 +8631,14 @@
         <is>
           <t>819443-2025</t>
         </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -8246,6 +8730,14 @@
         <is>
           <t>833026-2025</t>
         </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -8332,6 +8824,14 @@
           <t>833026-2025</t>
         </is>
       </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -8429,6 +8929,14 @@
           <t>53764-2026</t>
         </is>
       </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -8525,6 +9033,14 @@
         <is>
           <t>171806-2026</t>
         </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2449,100 +2449,106 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>10167000</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>37700001</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, Orifarm Generics A/S, Grindeks Kalceks Danmark ApS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Unimedic Pharma AB, Orifarm Generics A/S, Abcur AB</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>2024-02-15Z</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C47" s="3" t="n">
         <v>410000000</v>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Region Västernorrland</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2024-03-11Z</t>
         </is>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C48" s="1" t="n">
         <v>70000000</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Region Jönköpings Län</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12Z</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2552,35 +2558,29 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2024-04-24Z</t>
+          <t>2024-04-12Z</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>500000000</v>
+        <v>130000000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2590,87 +2590,87 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>2024-05-15Z</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C51" s="3" t="n">
         <v>268138000</v>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>447642000</v>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-07-17Z</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>1063000000</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>1063000000</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Zentiva Denmark ApS</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>DKK</t>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2024-07-17Z</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>10167000</v>
+        <v>1063000000</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2678,11 +2678,11 @@
         </is>
       </c>
       <c r="E52" s="1" t="n">
-        <v>37700001</v>
+        <v>1063000000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FrostPharma AB, Orifarm Generics A/S, Grindeks Kalceks Danmark ApS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Unimedic Pharma AB, Orifarm Generics A/S, Abcur AB</t>
+          <t>Zentiva Denmark ApS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -913,6 +913,44 @@
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>88200000</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Region Blekinge</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Exsitec AB</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
@@ -2494,93 +2532,99 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB, Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>2024-02-15Z</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C48" s="3" t="n">
         <v>410000000</v>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Region Västernorrland</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2024-03-11Z</t>
         </is>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C49" s="1" t="n">
         <v>70000000</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Region Jönköpings Län</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12Z</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2590,35 +2634,29 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2024-04-24Z</t>
+          <t>2024-04-12Z</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>500000000</v>
+        <v>130000000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2628,109 +2666,109 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>2024-05-15Z</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C52" s="3" t="n">
         <v>268138000</v>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>447642000</v>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>2024-07-17Z</t>
         </is>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C53" s="1" t="n">
         <v>1063000000</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Amgros I/S</t>
         </is>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E53" s="1" t="n">
         <v>1063000000</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Zentiva Denmark ApS</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>325000000</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>650000000</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB, Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>DKK</t>
         </is>
       </c>
     </row>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -955,6 +955,38 @@
           <t>SEK</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>247625623</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Almi AB</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ECIT Services AB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2602,93 +2602,99 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>13690000</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>MSD Danmark ApS, EQL Pharma AB, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, 2care4 ApS, Abcur AB, Abacus Medicine A/S, Orifarm A/S, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>2024-02-15Z</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C49" s="3" t="n">
         <v>410000000</v>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Region Västernorrland</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>2024-03-11Z</t>
         </is>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C50" s="1" t="n">
         <v>70000000</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Region Jönköpings Län</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12Z</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2698,35 +2704,29 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2024-04-24Z</t>
+          <t>2024-04-12Z</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>500000000</v>
+        <v>130000000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2736,107 +2736,107 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>2024-05-15Z</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C53" s="3" t="n">
         <v>268138000</v>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>447642000</v>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>2024-07-17Z</t>
         </is>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C54" s="1" t="n">
         <v>1063000000</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Amgros I/S</t>
         </is>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E54" s="1" t="n">
         <v>1063000000</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Zentiva Denmark ApS</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>13690000</v>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>MSD Danmark ApS, EQL Pharma AB, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, 2care4 ApS, Abcur AB, Abacus Medicine A/S, Orifarm A/S, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>DKK</t>
         </is>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2885,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6092,12 +6092,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel</t>
+          <t>Administrativa föreskrifter</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter</t>
+          <t>Kravspec Läkemedel</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6361,22 +6361,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
+          <t>Finnish Institute for Health and Welfare</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>LOT-0000</t>
+          <t>LOT-0004</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Läkemedel på rekvisition 2025 SLL450</t>
+          <t>LOT 4: Glycopyrrhonium/neostigmin 0,5/2,5 mg/ml (1 ml per vial/ampoule i.v. ATC N07AA51)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6388,43 +6388,27 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>332000000</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n">
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="S38" s="2" t="n">
-        <v>61</v>
       </c>
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
@@ -6434,42 +6418,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Sweden – Pharmaceutical products – Läkemedel på rekvisition 2025 SLL450</t>
+          <t>Finland – Medicinal products for the nervous system – Analgesics and anesthetics for systemic use</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>219864-2025</t>
+          <t>260803-2025</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Finnish Institute for Health and Welfare</t>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>LOT-0004</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>LOT 4: Glycopyrrhonium/neostigmin 0,5/2,5 mg/ml (1 ml per vial/ampoule i.v. ATC N07AA51)</t>
+          <t>Lot No. 1</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6477,31 +6461,59 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>11765767</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="S39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
@@ -6511,21 +6523,21 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Finland – Medicinal products for the nervous system – Analgesics and anesthetics for systemic use</t>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>260803-2025</t>
+          <t>375509-2025</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -6554,43 +6566,37 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="3" t="n">
+        <v>225775606</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>11765767</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="3" t="n">
+        <v>227000000</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
       <c r="N40" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
@@ -6616,12 +6622,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>375509-2025</t>
+          <t>376656-2025</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
@@ -6646,12 +6652,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 1</t>
+          <t>Lot No. 2</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6662,7 +6668,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>14000000</v>
+        <v>6200000</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -6745,12 +6751,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 2</t>
+          <t>Lot No. 3</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6758,10 +6764,16 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="3" t="n">
+        <v>12777840</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="n">
-        <v>6200000</v>
+        <v>136000000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -6844,12 +6856,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0004</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 3</t>
+          <t>Lot No. 4</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -6857,16 +6869,10 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>12777840</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="3" t="n">
-        <v>136000000</v>
+        <v>38000000</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -6909,7 +6915,7 @@
         <v>4</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr">
@@ -6933,28 +6939,28 @@
         </is>
       </c>
       <c r="Y43" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+          <t>Region Blekinge</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>LOT-0004</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 4</t>
+          <t>Läkemedel Cytostatika 2025</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6962,53 +6968,43 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="3" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
+      <c r="F44" s="3" t="n">
+        <v>24450368</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="3" t="n">
-        <v>225775606</v>
+        <v>30000000</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="L44" s="3" t="n">
-        <v>227000000</v>
+        <v>30000000</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2029-03-31</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr">
@@ -7018,12 +7014,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+          <t>Sweden – Pharmaceutical products – Läkemedel Cytostatika 2025</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>376656-2025</t>
+          <t>649606-2025</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
@@ -7032,28 +7028,28 @@
         </is>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Region Blekinge</t>
+          <t>Amgros I/S</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0012</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Läkemedel Cytostatika 2025</t>
+          <t>Udbudsnummer 12</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7062,42 +7058,58 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>24450368</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>5844466</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
       <c r="J45" s="3" t="n">
-        <v>30000000</v>
+        <v>370000000</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>30000000</v>
+        <v>245033539</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="S45" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr">
@@ -7107,12 +7119,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Sweden – Pharmaceutical products – Läkemedel Cytostatika 2025</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.700.a</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>649606-2025</t>
+          <t>683774-2025</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -7121,13 +7133,13 @@
         </is>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -7151,7 +7163,7 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0</v>
+        <v>1320000</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -7159,7 +7171,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>5844466</v>
+        <v>5638177</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -7167,7 +7179,7 @@
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>370000000</v>
+        <v>160000000</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -7175,7 +7187,7 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>245033539</v>
+        <v>66631361</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -7183,10 +7195,10 @@
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
@@ -7202,7 +7214,7 @@
         <v>3</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr">
@@ -7212,12 +7224,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.700.a</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>683774-2025</t>
+          <t>692426-2025</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -7226,7 +7238,7 @@
         </is>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -7347,12 +7359,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LOT-0012</t>
+          <t>LOT-0010</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 12</t>
+          <t>Udbudsnummer 10</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7361,7 +7373,7 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1320000</v>
+        <v>85000</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -7369,7 +7381,7 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5638177</v>
+        <v>1118087</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -7452,12 +7464,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>LOT-0010</t>
+          <t>LOT-0011</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 10</t>
+          <t>Udbudsnummer 11</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7466,7 +7478,7 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>85000</v>
+        <v>557000</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -7474,7 +7486,7 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>1118087</v>
+        <v>2328758</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7559,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7557,12 +7569,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>LOT-0011</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 11</t>
+          <t>Udbudsnummer 6</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7571,7 +7583,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>557000</v>
+        <v>447000</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -7579,7 +7591,7 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>2328758</v>
+        <v>525617</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -7587,7 +7599,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>160000000</v>
+        <v>20900000</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -7595,7 +7607,7 @@
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>66631361</v>
+        <v>13286794</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -7603,10 +7615,10 @@
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -7632,12 +7644,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>692426-2025</t>
+          <t>710534-2025</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
@@ -7662,12 +7674,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0019</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 6</t>
+          <t>Udbudsnummer 19</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7676,7 +7688,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>447000</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -7684,7 +7696,7 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>525617</v>
+        <v>4174341</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -7692,7 +7704,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>20900000</v>
+        <v>91400000</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -7700,7 +7712,7 @@
         </is>
       </c>
       <c r="L51" s="3" t="n">
-        <v>13286794</v>
+        <v>88050546</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -7708,10 +7720,10 @@
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -7737,12 +7749,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>710534-2025</t>
+          <t>712539-2025</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
@@ -7767,12 +7779,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>LOT-0019</t>
+          <t>LOT-0021</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 19</t>
+          <t>Udbudsnummer 21</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7789,7 +7801,7 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>4174341</v>
+        <v>6724462</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -7832,7 +7844,7 @@
         <v>3</v>
       </c>
       <c r="S52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr">
@@ -7856,13 +7868,13 @@
         </is>
       </c>
       <c r="Y52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -7872,12 +7884,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>LOT-0021</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 21</t>
+          <t>Udbudsnummer 6</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7894,7 +7906,7 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>6724462</v>
+        <v>12568724</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -7902,7 +7914,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>91400000</v>
+        <v>383000000</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -7910,7 +7922,7 @@
         </is>
       </c>
       <c r="L53" s="3" t="n">
-        <v>88050546</v>
+        <v>368505024</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -7918,10 +7930,10 @@
         </is>
       </c>
       <c r="N53" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -7937,7 +7949,7 @@
         <v>3</v>
       </c>
       <c r="S53" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr">
@@ -7947,12 +7959,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.1203.a</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>712539-2025</t>
+          <t>719210-2025</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
@@ -7961,13 +7973,13 @@
         </is>
       </c>
       <c r="Y53" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7977,12 +7989,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0021</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 6</t>
+          <t>Udbudsnummer 21</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7991,7 +8003,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0</v>
+        <v>670000</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -7999,7 +8011,7 @@
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>12568724</v>
+        <v>846850</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -8007,7 +8019,7 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>383000000</v>
+        <v>12200000</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -8015,7 +8027,7 @@
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>368505024</v>
+        <v>7867813</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -8023,10 +8035,10 @@
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
@@ -8042,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="S54" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
@@ -8052,12 +8064,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.1203.a</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.603.a</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>719210-2025</t>
+          <t>720704-2025</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
@@ -8066,7 +8078,7 @@
         </is>
       </c>
       <c r="Y54" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -8082,12 +8094,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>LOT-0021</t>
+          <t>LOT-0023</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 21</t>
+          <t>Udbudsnummer 23</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -8096,7 +8108,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>670000</v>
+        <v>137000</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -8104,7 +8116,7 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>846850</v>
+        <v>273738</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -8147,7 +8159,7 @@
         <v>3</v>
       </c>
       <c r="S55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr">
@@ -8171,13 +8183,13 @@
         </is>
       </c>
       <c r="Y55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -8187,12 +8199,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>LOT-0023</t>
+          <t>LOT-0005</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 23</t>
+          <t>Udbudsnummer 5</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -8201,7 +8213,7 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>137000</v>
+        <v>301000</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -8209,7 +8221,7 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>273738</v>
+        <v>991306</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8229,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>12200000</v>
+        <v>5040000</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -8225,7 +8237,7 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>7867813</v>
+        <v>4100779</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -8233,10 +8245,10 @@
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -8252,7 +8264,7 @@
         <v>3</v>
       </c>
       <c r="S56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
@@ -8262,12 +8274,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.603.a</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1303.b</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>720704-2025</t>
+          <t>726110-2025</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
@@ -8276,7 +8288,7 @@
         </is>
       </c>
       <c r="Y56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -8292,12 +8304,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>LOT-0005</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 5</t>
+          <t>Udbudsnummer 2</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -8306,7 +8318,7 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>301000</v>
+        <v>2690000</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -8314,7 +8326,7 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>991306</v>
+        <v>6329096</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -8322,7 +8334,7 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>5040000</v>
+        <v>33400000</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -8330,7 +8342,7 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>4100779</v>
+        <v>23945273</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -8338,7 +8350,7 @@
         </is>
       </c>
       <c r="N57" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>1</v>
@@ -8357,7 +8369,7 @@
         <v>3</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
@@ -8367,12 +8379,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1303.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1390.b</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>726110-2025</t>
+          <t>726119-2025</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
@@ -8381,7 +8393,7 @@
         </is>
       </c>
       <c r="Y57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -8397,12 +8409,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 2</t>
+          <t>Udbudsnummer 3</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -8411,7 +8423,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>2690000</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -8419,7 +8431,7 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>6329096</v>
+        <v>8124758</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -8427,7 +8439,7 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>33400000</v>
+        <v>178000000</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8447,7 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>23945273</v>
+        <v>161990275</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -8443,7 +8455,7 @@
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>1</v>
@@ -8462,7 +8474,7 @@
         <v>3</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
@@ -8472,12 +8484,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1390.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1302.b</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>726119-2025</t>
+          <t>726933-2025</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
@@ -8486,13 +8498,13 @@
         </is>
       </c>
       <c r="Y58" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -8502,12 +8514,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0007</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 3</t>
+          <t>Udbudsnummer 7</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -8524,7 +8536,7 @@
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>8124758</v>
+        <v>2686417</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -8532,7 +8544,7 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>178000000</v>
+        <v>37700000</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -8540,7 +8552,7 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>161990275</v>
+        <v>34240300</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -8548,7 +8560,7 @@
         </is>
       </c>
       <c r="N59" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>1</v>
@@ -8567,7 +8579,7 @@
         <v>3</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr">
@@ -8577,12 +8589,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1302.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.12.a</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>726933-2025</t>
+          <t>819443-2025</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
@@ -8591,28 +8603,28 @@
         </is>
       </c>
       <c r="Y59" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Amgros I/S</t>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>LOT-0007</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 7</t>
+          <t>Administrativa föreskrifter - Över tröskelvärde</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -8620,59 +8632,53 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="n">
-        <v>2686417</v>
+        <v>22000000</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>37700000</v>
+        <v>325000000</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="L60" s="3" t="n">
-        <v>34240300</v>
+        <v>325000000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2029-03-31</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="R60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S60" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
@@ -8682,12 +8688,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.12.a</t>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2025 del 2</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>819443-2025</t>
+          <t>833026-2025</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
@@ -8696,7 +8702,7 @@
         </is>
       </c>
       <c r="Y60" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
@@ -8712,12 +8718,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter - Över tröskelvärde</t>
+          <t>Kravspec Läkemedel (2)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -8727,14 +8733,8 @@
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="3" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="3" t="n">
         <v>325000000</v>
       </c>
@@ -8801,22 +8801,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+          <t>Amgros I/S</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel (2)</t>
+          <t>Udbudsnummer 1</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -8824,47 +8824,59 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>5080417</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
       <c r="J62" s="3" t="n">
-        <v>325000000</v>
+        <v>26000000</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="L62" s="3" t="n">
-        <v>325000000</v>
+        <v>26000000</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2029-03-31</t>
         </is>
       </c>
       <c r="R62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S62" s="2" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
@@ -8874,12 +8886,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Sweden – Pharmaceutical products – Läkemedel 2025 del 2</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1306.b</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>833026-2025</t>
+          <t>53764-2026</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
@@ -8888,18 +8900,18 @@
         </is>
       </c>
       <c r="Y62" s="2" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Amgros I/S</t>
+          <t>Region Kalmar Län</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -8909,7 +8921,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 1</t>
+          <t>Rekvisitionsläkemedel - ATC-kod N 2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -8922,54 +8934,54 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>5080417</v>
+        <v>58000000</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>26000000</v>
+        <v>48000000</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>26000000</v>
+        <v>58000000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="N63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2029-03-31</t>
+          <t>2030-02-28</t>
         </is>
       </c>
       <c r="R63" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr">
@@ -8979,12 +8991,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1306.b</t>
+          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel - ATC-kod N 2026 (Sydöstra-K)</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>53764-2026</t>
+          <t>171806-2026</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
@@ -8993,111 +9005,6 @@
         </is>
       </c>
       <c r="Y63" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Region Kalmar Län</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>LOT-0001</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Rekvisitionsläkemedel - ATC-kod N 2026</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Won</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>2030-02-28</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S64" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="T64" s="2" t="inlineStr"/>
-      <c r="U64" s="2" t="inlineStr">
-        <is>
-          <t>Contract Award Notice</t>
-        </is>
-      </c>
-      <c r="V64" s="2" t="inlineStr">
-        <is>
-          <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel - ATC-kod N 2026 (Sydöstra-K)</t>
-        </is>
-      </c>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>171806-2026</t>
-        </is>
-      </c>
-      <c r="X64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y64" s="2" t="n">
         <v>18</v>
       </c>
     </row>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2885,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y63"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6092,12 +6092,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter</t>
+          <t>Kravspec Läkemedel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel</t>
+          <t>Administrativa föreskrifter</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6361,22 +6361,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Finnish Institute for Health and Welfare</t>
+          <t>Region Stockholm - Serviceförvaltningen</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>LOT-0004</t>
+          <t>LOT-0000</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>LOT 4: Glycopyrrhonium/neostigmin 0,5/2,5 mg/ml (1 ml per vial/ampoule i.v. ATC N07AA51)</t>
+          <t>Läkemedel på rekvisition 2025 SLL450</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6388,27 +6388,43 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="n">
+        <v>332000000</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S38" s="2" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
@@ -6418,42 +6434,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Finland – Medicinal products for the nervous system – Analgesics and anesthetics for systemic use</t>
+          <t>Sweden – Pharmaceutical products – Läkemedel på rekvisition 2025 SLL450</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>260803-2025</t>
+          <t>219864-2025</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+          <t>Finnish Institute for Health and Welfare</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0004</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 1</t>
+          <t>LOT 4: Glycopyrrhonium/neostigmin 0,5/2,5 mg/ml (1 ml per vial/ampoule i.v. ATC N07AA51)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6461,59 +6477,31 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>11765767</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
       <c r="N39" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>2029-03-31</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
@@ -6523,21 +6511,21 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
+          <t>Finland – Medicinal products for the nervous system – Analgesics and anesthetics for systemic use</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>375509-2025</t>
+          <t>260803-2025</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -6566,10 +6554,16 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="H40" s="3" t="n">
-        <v>14000000</v>
+        <v>11800000</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6571,7 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>225775606</v>
+        <v>11765767</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -6585,7 +6579,7 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>227000000</v>
+        <v>11800000</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -6593,10 +6587,10 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
@@ -6622,12 +6616,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>376656-2025</t>
+          <t>375509-2025</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
@@ -6652,12 +6646,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 2</t>
+          <t>Lot No. 1</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6668,7 +6662,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>6200000</v>
+        <v>14000000</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -6751,12 +6745,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 3</t>
+          <t>Lot No. 2</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6764,16 +6758,10 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>12777840</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="3" t="n">
-        <v>136000000</v>
+        <v>6200000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -6856,12 +6844,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>LOT-0004</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 4</t>
+          <t>Lot No. 3</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -6869,10 +6857,16 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
+        <v>12777840</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="H43" s="3" t="n">
-        <v>38000000</v>
+        <v>136000000</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -6915,7 +6909,7 @@
         <v>4</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr">
@@ -6939,28 +6933,28 @@
         </is>
       </c>
       <c r="Y43" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Region Blekinge</t>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0004</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Läkemedel Cytostatika 2025</t>
+          <t>Lot No. 4</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6968,43 +6962,53 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>24450368</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="J44" s="3" t="n">
-        <v>30000000</v>
+        <v>225775606</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L44" s="3" t="n">
-        <v>30000000</v>
+        <v>227000000</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="S44" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr">
@@ -7014,12 +7018,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Sweden – Pharmaceutical products – Läkemedel Cytostatika 2025</t>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>649606-2025</t>
+          <t>376656-2025</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
@@ -7028,28 +7032,28 @@
         </is>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Amgros I/S</t>
+          <t>Region Blekinge</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>LOT-0012</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 12</t>
+          <t>Läkemedel Cytostatika 2025</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7058,58 +7062,42 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0</v>
+        <v>24450368</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>5844466</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="3" t="n">
-        <v>370000000</v>
+        <v>30000000</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>245033539</v>
+        <v>30000000</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2029-03-31</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr">
@@ -7119,12 +7107,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.700.a</t>
+          <t>Sweden – Pharmaceutical products – Läkemedel Cytostatika 2025</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>683774-2025</t>
+          <t>649606-2025</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -7133,13 +7121,13 @@
         </is>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -7163,7 +7151,7 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1320000</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -7171,7 +7159,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>5638177</v>
+        <v>5844466</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -7179,7 +7167,7 @@
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>160000000</v>
+        <v>370000000</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -7187,7 +7175,7 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>66631361</v>
+        <v>245033539</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -7195,10 +7183,10 @@
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
@@ -7214,7 +7202,7 @@
         <v>3</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr">
@@ -7224,12 +7212,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.700.a</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>692426-2025</t>
+          <t>683774-2025</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -7238,7 +7226,7 @@
         </is>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -7359,12 +7347,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LOT-0010</t>
+          <t>LOT-0012</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 10</t>
+          <t>Udbudsnummer 12</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7373,7 +7361,7 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>85000</v>
+        <v>1320000</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -7381,7 +7369,7 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1118087</v>
+        <v>5638177</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -7464,12 +7452,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>LOT-0011</t>
+          <t>LOT-0010</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 11</t>
+          <t>Udbudsnummer 10</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7478,7 +7466,7 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>557000</v>
+        <v>85000</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -7486,7 +7474,7 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2328758</v>
+        <v>1118087</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -7559,7 +7547,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -7569,12 +7557,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0011</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 6</t>
+          <t>Udbudsnummer 11</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7583,7 +7571,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>447000</v>
+        <v>557000</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -7591,7 +7579,7 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>525617</v>
+        <v>2328758</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -7599,7 +7587,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>20900000</v>
+        <v>160000000</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -7607,7 +7595,7 @@
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>13286794</v>
+        <v>66631361</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -7615,10 +7603,10 @@
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -7644,12 +7632,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.790.b</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>710534-2025</t>
+          <t>692426-2025</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
@@ -7674,12 +7662,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>LOT-0019</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 19</t>
+          <t>Udbudsnummer 6</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7688,7 +7676,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -7696,7 +7684,7 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>4174341</v>
+        <v>525617</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -7704,7 +7692,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>91400000</v>
+        <v>20900000</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -7712,7 +7700,7 @@
         </is>
       </c>
       <c r="L51" s="3" t="n">
-        <v>88050546</v>
+        <v>13286794</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -7720,10 +7708,10 @@
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -7749,12 +7737,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>712539-2025</t>
+          <t>710534-2025</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
@@ -7779,12 +7767,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>LOT-0021</t>
+          <t>LOT-0019</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 21</t>
+          <t>Udbudsnummer 19</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7801,7 +7789,7 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>6724462</v>
+        <v>4174341</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -7844,7 +7832,7 @@
         <v>3</v>
       </c>
       <c r="S52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr">
@@ -7868,13 +7856,13 @@
         </is>
       </c>
       <c r="Y52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -7884,12 +7872,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0021</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 6</t>
+          <t>Udbudsnummer 21</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7906,7 +7894,7 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12568724</v>
+        <v>6724462</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -7914,7 +7902,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>383000000</v>
+        <v>91400000</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -7922,7 +7910,7 @@
         </is>
       </c>
       <c r="L53" s="3" t="n">
-        <v>368505024</v>
+        <v>88050546</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -7930,10 +7918,10 @@
         </is>
       </c>
       <c r="N53" s="2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7937,7 @@
         <v>3</v>
       </c>
       <c r="S53" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr">
@@ -7959,12 +7947,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.1203.a</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>719210-2025</t>
+          <t>712539-2025</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
@@ -7973,13 +7961,13 @@
         </is>
       </c>
       <c r="Y53" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -7989,12 +7977,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>LOT-0021</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 21</t>
+          <t>Udbudsnummer 6</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8003,7 +7991,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>670000</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -8011,7 +7999,7 @@
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>846850</v>
+        <v>12568724</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -8019,7 +8007,7 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>12200000</v>
+        <v>383000000</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -8027,7 +8015,7 @@
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>7867813</v>
+        <v>368505024</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -8035,10 +8023,10 @@
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
@@ -8054,7 +8042,7 @@
         <v>3</v>
       </c>
       <c r="S54" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
@@ -8064,12 +8052,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.603.a</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.1203.a</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>720704-2025</t>
+          <t>719210-2025</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
@@ -8078,7 +8066,7 @@
         </is>
       </c>
       <c r="Y54" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -8094,12 +8082,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>LOT-0023</t>
+          <t>LOT-0021</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 23</t>
+          <t>Udbudsnummer 21</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -8108,7 +8096,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>137000</v>
+        <v>670000</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -8116,7 +8104,7 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>273738</v>
+        <v>846850</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -8159,7 +8147,7 @@
         <v>3</v>
       </c>
       <c r="S55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr">
@@ -8183,13 +8171,13 @@
         </is>
       </c>
       <c r="Y55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -8199,12 +8187,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>LOT-0005</t>
+          <t>LOT-0023</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 5</t>
+          <t>Udbudsnummer 23</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -8213,7 +8201,7 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>301000</v>
+        <v>137000</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -8221,7 +8209,7 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>991306</v>
+        <v>273738</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -8229,7 +8217,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>5040000</v>
+        <v>12200000</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -8237,7 +8225,7 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>4100779</v>
+        <v>7867813</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -8245,10 +8233,10 @@
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -8264,7 +8252,7 @@
         <v>3</v>
       </c>
       <c r="S56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
@@ -8274,12 +8262,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1303.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.603.a</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>726110-2025</t>
+          <t>720704-2025</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
@@ -8288,7 +8276,7 @@
         </is>
       </c>
       <c r="Y56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -8304,12 +8292,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0005</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 2</t>
+          <t>Udbudsnummer 5</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -8318,7 +8306,7 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>2690000</v>
+        <v>301000</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8314,7 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>6329096</v>
+        <v>991306</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -8334,7 +8322,7 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>33400000</v>
+        <v>5040000</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -8342,7 +8330,7 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>23945273</v>
+        <v>4100779</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -8350,7 +8338,7 @@
         </is>
       </c>
       <c r="N57" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>1</v>
@@ -8369,7 +8357,7 @@
         <v>3</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
@@ -8379,12 +8367,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1390.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1303.b</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>726119-2025</t>
+          <t>726110-2025</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
@@ -8393,7 +8381,7 @@
         </is>
       </c>
       <c r="Y57" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -8409,12 +8397,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 3</t>
+          <t>Udbudsnummer 2</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -8423,7 +8411,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>2690000</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -8431,7 +8419,7 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>8124758</v>
+        <v>6329096</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -8439,7 +8427,7 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>178000000</v>
+        <v>33400000</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -8447,7 +8435,7 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>161990275</v>
+        <v>23945273</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -8455,7 +8443,7 @@
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>1</v>
@@ -8474,7 +8462,7 @@
         <v>3</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
@@ -8484,12 +8472,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1302.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1390.b</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>726933-2025</t>
+          <t>726119-2025</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
@@ -8498,13 +8486,13 @@
         </is>
       </c>
       <c r="Y58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -8514,12 +8502,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>LOT-0007</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 7</t>
+          <t>Udbudsnummer 3</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -8536,7 +8524,7 @@
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>2686417</v>
+        <v>8124758</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -8544,7 +8532,7 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>37700000</v>
+        <v>178000000</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -8552,7 +8540,7 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>34240300</v>
+        <v>161990275</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -8560,7 +8548,7 @@
         </is>
       </c>
       <c r="N59" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>1</v>
@@ -8579,7 +8567,7 @@
         <v>3</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr">
@@ -8589,12 +8577,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 1.12.a</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1302.b</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>819443-2025</t>
+          <t>726933-2025</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
@@ -8603,28 +8591,28 @@
         </is>
       </c>
       <c r="Y59" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+          <t>Amgros I/S</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0007</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter - Över tröskelvärde</t>
+          <t>Udbudsnummer 7</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -8632,53 +8620,59 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
       <c r="H60" s="3" t="n">
-        <v>22000000</v>
+        <v>2686417</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>325000000</v>
+        <v>37700000</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="L60" s="3" t="n">
-        <v>325000000</v>
+        <v>34240300</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>2029-03-31</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S60" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-31</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>38</v>
       </c>
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
@@ -8688,12 +8682,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Sweden – Pharmaceutical products – Läkemedel 2025 del 2</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 1.12.a</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>833026-2025</t>
+          <t>819443-2025</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
@@ -8702,7 +8696,7 @@
         </is>
       </c>
       <c r="Y60" s="2" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -8718,12 +8712,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel (2)</t>
+          <t>Administrativa föreskrifter - Över tröskelvärde</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -8733,8 +8727,14 @@
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="H61" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
       <c r="J61" s="3" t="n">
         <v>325000000</v>
       </c>
@@ -8801,22 +8801,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Amgros I/S</t>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 1</t>
+          <t>Kravspec Läkemedel (2)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -8824,59 +8824,47 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>5080417</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="3" t="n">
-        <v>26000000</v>
+        <v>325000000</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="L62" s="3" t="n">
-        <v>26000000</v>
+        <v>325000000</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2029-03-31</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="R62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S62" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
@@ -8886,12 +8874,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1306.b</t>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2025 del 2</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>53764-2026</t>
+          <t>833026-2025</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
@@ -8900,18 +8888,18 @@
         </is>
       </c>
       <c r="Y62" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Region Kalmar Län</t>
+          <t>Amgros I/S</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -8921,7 +8909,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Rekvisitionsläkemedel - ATC-kod N 2026</t>
+          <t>Udbudsnummer 1</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -8934,54 +8922,54 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>58000000</v>
+        <v>5080417</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>48000000</v>
+        <v>26000000</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>58000000</v>
+        <v>26000000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="N63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2030-02-28</t>
+          <t>2029-03-31</t>
         </is>
       </c>
       <c r="R63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S63" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="S63" s="2" t="n">
-        <v>18</v>
       </c>
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr">
@@ -8991,20 +8979,125 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1306.b</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>53764-2026</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Region Kalmar Län</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Rekvisitionsläkemedel - ATC-kod N 2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>2030-02-28</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
           <t>Sweden – Pharmaceutical products – Rekvisitionsläkemedel - ATC-kod N 2026 (Sydöstra-K)</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
+      <c r="W64" s="2" t="inlineStr">
         <is>
           <t>171806-2026</t>
         </is>
       </c>
-      <c r="X63" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="n">
+      <c r="Y64" s="2" t="n">
         <v>18</v>
       </c>
     </row>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2874,6 +2874,44 @@
       </c>
       <c r="H55" s="2" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>840000000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag, Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2885,7 +2923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6092,12 +6130,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel</t>
+          <t>A. Utvärderingskriterium för delområde 1, 4, 28, 31-32, 34-38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6185,12 +6223,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter</t>
+          <t>Kravspec Läkemedel</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6278,12 +6316,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>A. Utvärderingskriterium för delområde 1, 4, 28, 31-32, 34-38</t>
+          <t>Administrativa föreskrifter</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -7242,12 +7280,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>LOT-0021</t>
+          <t>LOT-0010</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 21</t>
+          <t>Udbudsnummer 10</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -7256,7 +7294,7 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -7264,7 +7302,7 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>6546929</v>
+        <v>1118087</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -7307,7 +7345,7 @@
         <v>3</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr">
@@ -7331,7 +7369,7 @@
         </is>
       </c>
       <c r="Y47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -7347,12 +7385,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LOT-0012</t>
+          <t>LOT-0011</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 12</t>
+          <t>Udbudsnummer 11</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7361,7 +7399,7 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1320000</v>
+        <v>557000</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -7369,7 +7407,7 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5638177</v>
+        <v>2328758</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -7452,12 +7490,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>LOT-0010</t>
+          <t>LOT-0012</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 10</t>
+          <t>Udbudsnummer 12</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7466,7 +7504,7 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>85000</v>
+        <v>1320000</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -7474,7 +7512,7 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>1118087</v>
+        <v>5638177</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -7557,12 +7595,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>LOT-0011</t>
+          <t>LOT-0021</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 11</t>
+          <t>Udbudsnummer 21</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7571,7 +7609,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>557000</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -7579,7 +7617,7 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>2328758</v>
+        <v>6546929</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -7622,7 +7660,7 @@
         <v>3</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr">
@@ -7646,7 +7684,7 @@
         </is>
       </c>
       <c r="Y50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -7662,12 +7700,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0021</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 6</t>
+          <t>Udbudsnummer 21</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7676,7 +7714,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>447000</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -7684,7 +7722,7 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>525617</v>
+        <v>6724462</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -7692,7 +7730,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>20900000</v>
+        <v>91400000</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -7700,7 +7738,7 @@
         </is>
       </c>
       <c r="L51" s="3" t="n">
-        <v>13286794</v>
+        <v>88050546</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -7708,10 +7746,10 @@
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -7727,7 +7765,7 @@
         <v>3</v>
       </c>
       <c r="S51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
@@ -7737,12 +7775,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>710534-2025</t>
+          <t>712539-2025</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
@@ -7751,7 +7789,7 @@
         </is>
       </c>
       <c r="Y51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -7767,12 +7805,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>LOT-0019</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 19</t>
+          <t>Udbudsnummer 6</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7781,7 +7819,7 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -7789,7 +7827,7 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>4174341</v>
+        <v>525617</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -7797,7 +7835,7 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>91400000</v>
+        <v>20900000</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -7805,7 +7843,7 @@
         </is>
       </c>
       <c r="L52" s="3" t="n">
-        <v>88050546</v>
+        <v>13286794</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7851,10 @@
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -7842,12 +7880,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Denmark – Pharmaceutical products – Amgros 2026 2.290.b</t>
+          <t>Denmark – Pharmaceutical products – Amgros 2026 2.1290.b</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>712539-2025</t>
+          <t>710534-2025</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
@@ -7872,12 +7910,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>LOT-0021</t>
+          <t>LOT-0019</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Udbudsnummer 21</t>
+          <t>Udbudsnummer 19</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7894,7 +7932,7 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>6724462</v>
+        <v>4174341</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -7937,7 +7975,7 @@
         <v>3</v>
       </c>
       <c r="S53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr">
@@ -7961,7 +7999,7 @@
         </is>
       </c>
       <c r="Y53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -9101,6 +9139,204 @@
         <v>18</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Kravspec Läkemedel</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2026 del 1</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>403318-2026</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>LOT-0002</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Administrativa föreskrifter</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="3" t="n">
+        <v>488000000</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Sweden – Pharmaceutical products – Läkemedel 2026 del 1</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>403318-2026</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="n">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2678,93 +2678,93 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2024-02-15Z</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>410000000</v>
+        <v>0</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Region Västernorrland</t>
+          <t>Region Kalmar Län</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
+          <t>Orifarm Generics AB, B Braun Medical AB, SUN Pharmaceuticals GmbH, Baxter Medical AB, Aspen Pharma Ireland Limited, Grindeks Kalceks Sverige AB, AGUETTANT NORDIC ApS, EQL Pharma AB, Camurus AB, Viatris AB, Fresenius Kabi, Haleon Sweden AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-15Z</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>2024-03-11Z</t>
         </is>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C51" s="1" t="n">
         <v>70000000</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Region Jönköpings Län</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12Z</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2774,35 +2774,29 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2024-04-24Z</t>
+          <t>2024-04-12Z</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>500000000</v>
+        <v>130000000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2812,105 +2806,111 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>2024-05-15Z</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C54" s="3" t="n">
         <v>268138000</v>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>447642000</v>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>2024-07-17Z</t>
         </is>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C55" s="1" t="n">
         <v>1063000000</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Amgros I/S</t>
         </is>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E55" s="1" t="n">
         <v>1063000000</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Zentiva Denmark ApS</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Region Kalmar Län</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Orifarm Generics AB, B Braun Medical AB, SUN Pharmaceuticals GmbH, Baxter Medical AB, Aspen Pharma Ireland Limited, Grindeks Kalceks Sverige AB, AGUETTANT NORDIC ApS, EQL Pharma AB, Camurus AB, Viatris AB, Fresenius Kabi, Haleon Sweden AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1025,6 +1025,38 @@
           <t>SEK</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Karlstads universitet</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolibri Vision AB</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -921,7 +921,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1057,6 +1057,44 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Svenska Institutet</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NoAIgnite AB</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -959,7 +959,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exsitec AB" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQL Pharma AB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQL Pharma AB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exsitec AB" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQL Pharma AB Detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -421,6 +421,1930 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Publication Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Awarded Value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Buyer Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Estimated Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Winner Name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Awarded Currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Estimated Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2021-11-02</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Region Halland</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Region Halland</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>64100000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2022-12-13</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>740437852</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Region Stockholm</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>85550000</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Region Jönköpings Län</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>2820000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>8520000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>3710000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>33500000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>67900000</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>167000000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2023-12-12</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>283949000</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>5515497000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, CSL Behring Aktiebolag, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, medac, Nordic Drugs Aktiebolag, Norgine A/S, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, CSL Behring Aktiebolag, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, medac, Nordic Drugs Aktiebolag, Norgine A/S, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, Nordic Drugs Aktiebolag, Norgine A/S, Pfizer Aktiebolag, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, CSL Behring Aktiebolag, Fresenius Kabi AB, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Roche Aktiebolag, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Baxter Medical AB, betapharm Arzneimittel GmbH, FrostPharma AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, medac, Roche Aktiebolag, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, betapharm Arzneimittel GmbH, Fresenius Kabi AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Sandoz A/S, Sun Pharmaceutical Germany GmbH</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>35886000</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Aguettant Nordic ApS, Macure Pharma ApS, Unimedic Pharma AB, Aguettant Nordic ApS, Abboxia AB, Øresund Pharma ApS, Abacus Medicine A/S, Orifarm A/S, Zentiva Denmark ApS, Accord Healthcare AB, 2care4 ApS, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>12855000</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>34600003</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Medical Valley Invest AB, Orifarm Generics A/S, Sandoz A/S, Haleon Denmark ApS, Medical Valley Invest AB, Krka Sverige AB, Sandoz A/S, Orifarm Generics A/S, Haleon Denmark ApS, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Orifarm Generics A/S, Teva Denmark A/S, Orifarm Generics A/S, Teva Denmark A/S, Orifarm Generics A/S, Teva Denmark A/S, Macure Pharma ApS, Macure Pharma ApS, Macure Pharma ApS, Macure Pharma ApS, EQL Pharma AB, EQL Pharma AB, Orifarm Generics A/S</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>9080000</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Orifarm Generics A/S, Grünenthal Denmark ApS, Teva Denmark A/S, Medical Valley Invest AB, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4927000</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20899997</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, Haleon Denmark ApS, Haleon Denmark ApS, EQL Pharma AB, Abcur AB, Hameln Pharma ApS, Øresund Pharma ApS, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>68731000</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>96100002</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Jazz Pharmaceuticals Denmark ApS, Sandoz A/S, Medical Valley Invest AB, Sandoz A/S, Sandoz A/S, Chiesi Pharma AB, 2care4 ApS, 2care4 ApS, Haleon Denmark ApS, Haleon Denmark ApS, Haleon Denmark ApS, McNeil Denmark ApS, McNeil Denmark ApS, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>56597000</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>129999998</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Panpharma Nordic AS, Panpharma Nordic AS, Sandoz A/S, EQL Pharma AB, Panpharma Nordic AS, Stragen Nordic A/S, Navamedic AB, Macure Pharma ApS, Stragen Nordic A/S, Navamedic AB, Macure Pharma ApS, XGX Pharma ApS, 2care4 ApS, Macure Pharma ApS, Fresenius Kabi, Navamedic AB, Pfizer ApS, Sun Pharmaceuticals Germany GmbH, MSD Danmark ApS, Orifarm A/S, 2care4 ApS, MSD Danmark ApS, Hameln Pharma ApS, Orifarm Generics A/S, Orifarm A/S, FrostPharma AB, Accord Healthcare AB, Hameln Pharma ApS, MSD Danmark ApS</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>35346000</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>80099999</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Sandoz A/S, 2care4 ApS, Sandoz A/S, 2care4 ApS, 2care4 ApS, Sandoz A/S, Orion Pharma A/S, Karo Healthcare AB, Orion Pharma A/S, Orion Pharma A/S, Karo Healthcare AB, EQL Pharma AB, Sandoz A/S, 2care4 ApS, 2care4 ApS, Sandoz A/S, 2care4 ApS, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orifarm Generics A/S, Krka Sverige AB, Sandoz A/S, 2care4 ApS, Krka Sverige AB, Krka Sverige AB, Sandoz A/S, 2care4 ApS, Accord Healthcare AB, 2care4 ApS, Teva Denmark A/S, STADA Nordic ApS, Krka Sverige AB, Teva Denmark A/S, STADA Nordic ApS, Krka Sverige AB, Krka Sverige AB, Pfizer ApS, Orifarm Generics A/S, Pfizer ApS, STADA Nordic ApS, STADA Nordic ApS, Krka Sverige AB, STADA Nordic ApS, Krka Sverige AB, Orion Pharma A/S, Krka Sverige AB, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Finnish Institute for Health and Welfare</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, Orion Oyj, Orion Oyj, EQL Pharma AB, Orion Oyj</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Vankiterveydenhuollon yksikkö, Niuvanniemen sairaala, Vanhan Vaasan sairaala</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Ailon Pharma Oy, Aguettant Nordic ApS, Avansor Pharma Oy, Bausch Lomb Nordic, Bayer Oy, Berner Oy, B. Braun Medical Oy, Camurus AB, DNE PHARMA AS, EQL Pharma AB, Essential Pharma Limited, Exeltis Sverige AB, filial i Finland, Fresenius Kabi Ab, FrostPharma AB, Gedeon Richter Nordics Ab, Grindeks Kalceks Suomi Oy, Haleon Finland Oy, Indivior Europe Limited, Krka Finland Oy, Mediq Suomi Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy Eli Lilly Finland Ab, Oy Verman Ab, Pierrel S.p.A., Teva Finland Oy, Viatris Oy, Ailon Pharma Oy, Avansor Pharma Oy, Bausch Lomb Nordic, Bayer Oy, CNX Therapeutics Ltd., DNE PHARMA AS, Essential Pharma Limited, Grindeks Kalceks Suomi Oy, Haleon Finland Oy, Indivior Europe Limited, Krka Finland Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy H. Lundbeck Ab, Oy Verman Ab, TD Pharma B.V., Teva Finland Oy, Viatris Oy</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>233084078</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1920000000</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Accord Healthcare AB, betapharm Arzneimittel GmbH, CAMPUS Pharma AB, EQL Pharma AB, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Medical Valley Invest AB, Orifarm Generics AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, betapharm Arzneimittel GmbH, CAMPUS Pharma AB, EQL Pharma AB, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Medical Valley Invest AB, Orifarm Generics AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, betapharm Arzneimittel GmbH, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, Sandoz A/S, Accord Healthcare AB, Fresenius Kabi AB, Macure Pharma, Medical Valley Invest AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, CAMPUS Pharma AB</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>4128000000</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>G.L. Pharma Nordic Aktiebolag, Amgen Aktiebolag, Novartis Sverige Aktiebolag, Galenica AB, Mölnlycke Health Care AB, Evolan Pharma AB, AstraZeneca AB, dne pharma as, Sandoz A/S, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Pharmacosmos A/S, Norgine A/S, Octapharma Nordic AB, Aspen Pharma Ireland Limited, Fresenius Kabi AB, Scandinavian Biopharma Distribution AB, Unimedic Pharma AB, B.Braun Medical AB, Bracco Imaging Scandinavia AB, Baxter Medical AB, hameln pharma AB, Viatris AB, Pfizer Aktiebolag, Orifarm AB, CSL Behring Aktiebolag, Orifarm Generics AB, Biogen Sweden AB, Abcur AB, FrostPharma AB, Teva Sweden Aktiebolag, Roche Aktiebolag, Aguettant Nordic ApS, Grifols Nordic AB, Vifor Pharma Nordiska AB, Recordati AB, Accord Healthcare AB, CAMPUS Pharma AB, Grindeks Kalceks Sverige AB, Macure Pharma, Takeda Pharma AB, Tillotts Pharma AB, Bausch &amp; Lomb Nordic AB, Sanofi AB, Bluefish Pharmaceuticals AB (publ), Abboxia AB, Bayer Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Finnish Institute for Health and Welfare</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Grindeks Kalceks Suomi Oy, Grindeks Kalceks Suomi Oy, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3256789</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>11765767</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>EQL Pharma AB, Navamedic AB, FrostPharma AB</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>33696648</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>225775646</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, STADA Nordic ApS, EQL Pharma AB, Fresenius Kabi, Navamedic AB, Navamedic AB, Navamedic AB, Fresenius Kabi, B. Braun Medical AS, B. Braun Medical A/S, B. Braun Medical AS, B. Braun Medical A/S, B. Braun Medical AS, B. Braun Medical A/S, Fresenius Kabi, Navamedic AB, Hameln Pharma ApS, Orion Pharma A/S</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>513457728</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Region Blekinge</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Amgen Aktiebolag, Orifarm AB, Baxter Medical Aktiebolag, Roche Aktiebolag, Orifarm Generics AB, Grindeks Kalceks Sverige AB, Sandoz A/S, STADA Nordic ApS, Biosimilar Collaborations Ireland Limited, CAMPUS Pharma AB, betapharm Arzneimittel GmbH, Accord Healthcare AB, Glenmark Pharmaceuticals Nordic AB, Fresenius Kabi AB</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>115014000</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>370000003</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grindeks Kalceks Danmark ApS, Grindeks Kalceks Danmark ApS, 2care4 Generics ApS, G.L. Pharma Nordic Aktiebolag, STADA Nordic ApS, STADA Nordic ApS, Orifarm Generics A/S, Sandoz A/S, Grindeks Kalceks Danmark ApS, Swedish Orphan Biovitrum AB, STADA Nordic ApS, Recordati AB, McNeil Denmark ApS, Vifor Pharma Nordiska AB, STADA Nordic ApS, Vifor Pharma Nordiska AB, Orifarm Generics A/S, Viatris ApS, Abacus Medicine A/S, Abcur AB, BioMarin International Limited, Immedica Pharma AB, Amicus Therapeutics Europe Limited, Nordic Prime ApS, Takeda Pharma A/S, Takeda Pharma A/S</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>41562000</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Teva Denmark A/S, STADA Nordic ApS, STADA Nordic ApS, Krka Sverige AB, Teva Denmark A/S, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Sandoz A/S, Sandoz A/S, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Krka Sverige AB, Øresund Pharma ApS, Krka Sverige AB, Krka Sverige AB, Øresund Pharma ApS, Krka Sverige AB, Abacus Medicine A/S, Orifarm A/S, EQL Pharma AB, STADA Nordic ApS, EQL Pharma AB, STADA Nordic ApS, EQL Pharma AB, STADA Nordic ApS, Orifarm Generics A/S, McNeil Denmark ApS, Boehringer Ingelheim Danmark A/S, Boehringer Ingelheim Danmark A/S, Strides Nordic ApS, Strides Nordic ApS, 2care4 ApS, Strides Nordic ApS, Paranova Danmark A/S, Abacus Medicine A/S, Karo Healthcare AB, Orifarm Generics A/S, EQL Pharma AB</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5579000</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>20900000</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, EQL Pharma AB, Orifarm Generics A/S, Recordati AB, Krka Sverige AB, Sandoz A/S, Recordati AB, Viatris ApS, Krka Sverige AB, Recordati AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>43084000</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>91400000</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Krka Sverige AB, Sandoz A/S, STADA Nordic ApS, Sanofi A/S, Orifarm Generics A/S, Teva Denmark A/S, Sandoz A/S, Teva Denmark A/S, Orifarm Generics A/S, 2care4 Generics ApS, Viatris ApS, 2care4 ApS, Zentiva Denmark ApS, Orifarm A/S, Zentiva Denmark ApS, Krka Sverige AB, Zentiva Denmark ApS, Orifarm Generics A/S, Krka Sverige AB, Zentiva Denmark ApS, Orifarm Generics A/S, EQL Pharma AB, Orifarm Generics A/S, Teva Denmark A/S, EQL Pharma AB, Abacus Medicine A/S, Takeda Pharma A/S, Takeda Pharma A/S, Abacus Medicine A/S, Strides Nordic ApS, Omet Pharma AB, Orifarm Generics A/S, Strides Nordic ApS, Omet Pharma AB, STADA Nordic ApS, STADA Nordic ApS, STADA Nordic ApS, Sandoz A/S, Orifarm Generics A/S, Teva Denmark A/S, Sandoz A/S, Orifarm Generics A/S, Teva Denmark A/S</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>32792000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>LEO Pharma A/S, Mundipharma A/S, Pharmanovia A/S, Pharmanovia A/S, Øresund Pharma ApS, Orifarm Generics A/S, Paranova Danmark A/S, 2care4 ApS, Abacus Medicine A/S, Abacus Medicine A/S, Orifarm A/S, CampusPharma AB, SERB SAS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>6020000</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>12200001</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2care4 Generics ApS, Haleon Denmark ApS, Haleon Denmark ApS, Haleon Denmark ApS, Teva Denmark A/S, EQL Pharma AB, EQL Pharma AB, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1860000</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>5040002</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Paranova Danmark A/S, Orifarm A/S, 2care4 Generics ApS, EQL Pharma AB, 2care4 Generics ApS, Viatris ApS</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>8465000</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>33399999</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Viatris ApS, EQL Pharma AB, Orifarm Generics A/S, Viatris ApS, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orion Pharma A/S, Orifarm Generics A/S, 2care4 ApS, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Teva Denmark A/S, Pfizer ApS, Krka Sverige AB, Sandoz A/S, STADA Nordic ApS, Krka Sverige AB, Orifarm A/S, Sandoz A/S, Paranova Danmark A/S, 2care4 ApS, Orifarm A/S, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>38466000</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>178000002</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Panpharma Nordic AS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Panpharma Nordic AS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Panpharma Nordic AS, EQL Pharma AB, Sandoz A/S, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Navamedic AB, Navamedic AB, Panpharma Nordic AS, Abcur AB, Macure Pharma ApS, Grindeks Kalceks Danmark ApS, Hameln Pharma ApS, Pfizer ApS, Abcur AB, Panpharma Nordic AS, Sandoz A/S, Sandoz A/S, Macure Pharma ApS, Orifarm A/S, 2care4 ApS, Orifarm A/S, 2care4 ApS, Abacus Medicine A/S</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>10167000</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>37700001</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FrostPharma AB, Orifarm Generics A/S, Grindeks Kalceks Danmark ApS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Unimedic Pharma AB, Orifarm Generics A/S, Abcur AB</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>325000000</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB, Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>13690000</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>MSD Danmark ApS, EQL Pharma AB, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, 2care4 ApS, Abcur AB, Abacus Medicine A/S, Orifarm A/S, 2care4 ApS</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Region Kalmar Län</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Orifarm Generics AB, B Braun Medical AB, SUN Pharmaceuticals GmbH, Baxter Medical AB, Aspen Pharma Ireland Limited, Grindeks Kalceks Sverige AB, AGUETTANT NORDIC ApS, EQL Pharma AB, Camurus AB, Viatris AB, Fresenius Kabi, Haleon Sweden AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-15Z</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Region Västernorrland</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2024-03-11Z</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Region Jönköpings Län</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-12Z</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-15Z</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>268138000</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>447642000</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2024-07-17Z</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Zentiva Denmark ApS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>840000000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag, Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1091,1930 +3015,6 @@
         </is>
       </c>
       <c r="H19" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Publication Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Awarded Value</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Buyer Name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Estimated Value</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Winner Name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Awarded Currency</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Estimated Currency</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2022-07-04</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Region Halland</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Region Halland</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>4980000</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>13300000</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>64100000</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2022-12-13</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>740437852</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Region Västernorrland</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023-03-10</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>2000000000</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Region Stockholm</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>85550000</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Region Jönköpings Län</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>2820000</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>8520000</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>3710000</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>33500000</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>67900000</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2023-10-20</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>167000000</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2023-12-01</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2023-12-12</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>283949000</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>5515497000</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, CSL Behring Aktiebolag, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, medac, Nordic Drugs Aktiebolag, Norgine A/S, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, CSL Behring Aktiebolag, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, medac, Nordic Drugs Aktiebolag, Norgine A/S, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, betapharm Arzneimittel GmbH, Bioglan AB, Camurus AB, dne pharma as, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Macure Pharma, Nordic Drugs Aktiebolag, Norgine A/S, Pfizer Aktiebolag, Sun Pharmaceutical Germany GmbH, Teva Sweden Aktiebolag, Accord Healthcare AB, CSL Behring Aktiebolag, Fresenius Kabi AB, Novartis Sverige Aktiebolag, Octapharma Nordic AB, Roche Aktiebolag, Scandinavian Biopharma Distribution AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Baxter Medical AB, betapharm Arzneimittel GmbH, FrostPharma AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, medac, Roche Aktiebolag, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, betapharm Arzneimittel GmbH, Fresenius Kabi AB, Sun Pharmaceutical Germany GmbH, Accord Healthcare AB, Sandoz A/S, Sun Pharmaceutical Germany GmbH</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>35886000</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>119000000</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Aguettant Nordic ApS, Macure Pharma ApS, Unimedic Pharma AB, Aguettant Nordic ApS, Abboxia AB, Øresund Pharma ApS, Abacus Medicine A/S, Orifarm A/S, Zentiva Denmark ApS, Accord Healthcare AB, 2care4 ApS, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>12855000</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>34600003</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Medical Valley Invest AB, Orifarm Generics A/S, Sandoz A/S, Haleon Denmark ApS, Medical Valley Invest AB, Krka Sverige AB, Sandoz A/S, Orifarm Generics A/S, Haleon Denmark ApS, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, Teva Denmark A/S, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Orifarm Generics A/S, Teva Denmark A/S, Orifarm Generics A/S, Teva Denmark A/S, Orifarm Generics A/S, Teva Denmark A/S, Macure Pharma ApS, Macure Pharma ApS, Macure Pharma ApS, Macure Pharma ApS, EQL Pharma AB, EQL Pharma AB, Orifarm Generics A/S</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>9080000</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Orifarm Generics A/S, Grünenthal Denmark ApS, Teva Denmark A/S, Medical Valley Invest AB, EQL Pharma AB</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>4927000</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>20899997</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, G.L. Pharma Nordic Aktiebolag, Haleon Denmark ApS, Haleon Denmark ApS, EQL Pharma AB, Abcur AB, Hameln Pharma ApS, Øresund Pharma ApS, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>68731000</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>96100002</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Jazz Pharmaceuticals Denmark ApS, Sandoz A/S, Medical Valley Invest AB, Sandoz A/S, Sandoz A/S, Chiesi Pharma AB, 2care4 ApS, 2care4 ApS, Haleon Denmark ApS, Haleon Denmark ApS, Haleon Denmark ApS, McNeil Denmark ApS, McNeil Denmark ApS, EQL Pharma AB</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>56597000</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>129999998</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Panpharma Nordic AS, Panpharma Nordic AS, Sandoz A/S, EQL Pharma AB, Panpharma Nordic AS, Stragen Nordic A/S, Navamedic AB, Macure Pharma ApS, Stragen Nordic A/S, Navamedic AB, Macure Pharma ApS, XGX Pharma ApS, 2care4 ApS, Macure Pharma ApS, Fresenius Kabi, Navamedic AB, Pfizer ApS, Sun Pharmaceuticals Germany GmbH, MSD Danmark ApS, Orifarm A/S, 2care4 ApS, MSD Danmark ApS, Hameln Pharma ApS, Orifarm Generics A/S, Orifarm A/S, FrostPharma AB, Accord Healthcare AB, Hameln Pharma ApS, MSD Danmark ApS</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>35346000</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>80099999</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Sandoz A/S, 2care4 ApS, Sandoz A/S, 2care4 ApS, 2care4 ApS, Sandoz A/S, Orion Pharma A/S, Karo Healthcare AB, Orion Pharma A/S, Orion Pharma A/S, Karo Healthcare AB, EQL Pharma AB, Sandoz A/S, 2care4 ApS, 2care4 ApS, Sandoz A/S, 2care4 ApS, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orifarm Generics A/S, Krka Sverige AB, Sandoz A/S, 2care4 ApS, Krka Sverige AB, Krka Sverige AB, Sandoz A/S, 2care4 ApS, Accord Healthcare AB, 2care4 ApS, Teva Denmark A/S, STADA Nordic ApS, Krka Sverige AB, Teva Denmark A/S, STADA Nordic ApS, Krka Sverige AB, Krka Sverige AB, Pfizer ApS, Orifarm Generics A/S, Pfizer ApS, STADA Nordic ApS, STADA Nordic ApS, Krka Sverige AB, STADA Nordic ApS, Krka Sverige AB, Orion Pharma A/S, Krka Sverige AB, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Finnish Institute for Health and Welfare</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>FrostPharma AB, Orion Oyj, Orion Oyj, EQL Pharma AB, Orion Oyj</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Vankiterveydenhuollon yksikkö, Niuvanniemen sairaala, Vanhan Vaasan sairaala</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Ailon Pharma Oy, Aguettant Nordic ApS, Avansor Pharma Oy, Bausch Lomb Nordic, Bayer Oy, Berner Oy, B. Braun Medical Oy, Camurus AB, DNE PHARMA AS, EQL Pharma AB, Essential Pharma Limited, Exeltis Sverige AB, filial i Finland, Fresenius Kabi Ab, FrostPharma AB, Gedeon Richter Nordics Ab, Grindeks Kalceks Suomi Oy, Haleon Finland Oy, Indivior Europe Limited, Krka Finland Oy, Mediq Suomi Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy Eli Lilly Finland Ab, Oy Verman Ab, Pierrel S.p.A., Teva Finland Oy, Viatris Oy, Ailon Pharma Oy, Avansor Pharma Oy, Bausch Lomb Nordic, Bayer Oy, CNX Therapeutics Ltd., DNE PHARMA AS, Essential Pharma Limited, Grindeks Kalceks Suomi Oy, Haleon Finland Oy, Indivior Europe Limited, Krka Finland Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy H. Lundbeck Ab, Oy Verman Ab, TD Pharma B.V., Teva Finland Oy, Viatris Oy</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>233084078</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>1920000000</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Accord Healthcare AB, betapharm Arzneimittel GmbH, CAMPUS Pharma AB, EQL Pharma AB, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Medical Valley Invest AB, Orifarm Generics AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, betapharm Arzneimittel GmbH, CAMPUS Pharma AB, EQL Pharma AB, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Medical Valley Invest AB, Orifarm Generics AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, betapharm Arzneimittel GmbH, Fresenius Kabi AB, hameln pharma AB, Macure Pharma, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, Accord Healthcare AB, Sandoz A/S, Accord Healthcare AB, Fresenius Kabi AB, Macure Pharma, Medical Valley Invest AB, Pfizer Aktiebolag, Roche Aktiebolag, Sandoz A/S, Sun Pharmaceutical Germany GmbH, Øresund Pharma ApS, CAMPUS Pharma AB</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>4128000000</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>G.L. Pharma Nordic Aktiebolag, Amgen Aktiebolag, Novartis Sverige Aktiebolag, Galenica AB, Mölnlycke Health Care AB, Evolan Pharma AB, AstraZeneca AB, dne pharma as, Sandoz A/S, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Pharmacosmos A/S, Norgine A/S, Octapharma Nordic AB, Aspen Pharma Ireland Limited, Fresenius Kabi AB, Scandinavian Biopharma Distribution AB, Unimedic Pharma AB, B.Braun Medical AB, Bracco Imaging Scandinavia AB, Baxter Medical AB, hameln pharma AB, Viatris AB, Pfizer Aktiebolag, Orifarm AB, CSL Behring Aktiebolag, Orifarm Generics AB, Biogen Sweden AB, Abcur AB, FrostPharma AB, Teva Sweden Aktiebolag, Roche Aktiebolag, Aguettant Nordic ApS, Grifols Nordic AB, Vifor Pharma Nordiska AB, Recordati AB, Accord Healthcare AB, CAMPUS Pharma AB, Grindeks Kalceks Sverige AB, Macure Pharma, Takeda Pharma AB, Tillotts Pharma AB, Bausch &amp; Lomb Nordic AB, Sanofi AB, Bluefish Pharmaceuticals AB (publ), Abboxia AB, Bayer Aktiebolag</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Finnish Institute for Health and Welfare</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Grindeks Kalceks Suomi Oy, Grindeks Kalceks Suomi Oy, EQL Pharma AB</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>3256789</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>11765767</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>EQL Pharma AB, Navamedic AB, FrostPharma AB</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>33696648</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S, Landspítali Háskólasjúkrahús, Sykehusinnkjøp HF, divisjon legemidler</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>225775646</v>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>FrostPharma AB, STADA Nordic ApS, EQL Pharma AB, Fresenius Kabi, Navamedic AB, Navamedic AB, Navamedic AB, Fresenius Kabi, B. Braun Medical AS, B. Braun Medical A/S, B. Braun Medical AS, B. Braun Medical A/S, B. Braun Medical AS, B. Braun Medical A/S, Fresenius Kabi, Navamedic AB, Hameln Pharma ApS, Orion Pharma A/S</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>513457728</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Region Blekinge</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Amgen Aktiebolag, Orifarm AB, Baxter Medical Aktiebolag, Roche Aktiebolag, Orifarm Generics AB, Grindeks Kalceks Sverige AB, Sandoz A/S, STADA Nordic ApS, Biosimilar Collaborations Ireland Limited, CAMPUS Pharma AB, betapharm Arzneimittel GmbH, Accord Healthcare AB, Glenmark Pharmaceuticals Nordic AB, Fresenius Kabi AB</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>115014000</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>370000003</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Grindeks Kalceks Danmark ApS, Grindeks Kalceks Danmark ApS, 2care4 Generics ApS, G.L. Pharma Nordic Aktiebolag, STADA Nordic ApS, STADA Nordic ApS, Orifarm Generics A/S, Sandoz A/S, Grindeks Kalceks Danmark ApS, Swedish Orphan Biovitrum AB, STADA Nordic ApS, Recordati AB, McNeil Denmark ApS, Vifor Pharma Nordiska AB, STADA Nordic ApS, Vifor Pharma Nordiska AB, Orifarm Generics A/S, Viatris ApS, Abacus Medicine A/S, Abcur AB, BioMarin International Limited, Immedica Pharma AB, Amicus Therapeutics Europe Limited, Nordic Prime ApS, Takeda Pharma A/S, Takeda Pharma A/S</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>41562000</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>160000000</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Teva Denmark A/S, STADA Nordic ApS, STADA Nordic ApS, Krka Sverige AB, Teva Denmark A/S, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Sandoz A/S, Sandoz A/S, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Krka Sverige AB, Øresund Pharma ApS, Krka Sverige AB, Krka Sverige AB, Øresund Pharma ApS, Krka Sverige AB, Abacus Medicine A/S, Orifarm A/S, EQL Pharma AB, STADA Nordic ApS, EQL Pharma AB, STADA Nordic ApS, EQL Pharma AB, STADA Nordic ApS, Orifarm Generics A/S, McNeil Denmark ApS, Boehringer Ingelheim Danmark A/S, Boehringer Ingelheim Danmark A/S, Strides Nordic ApS, Strides Nordic ApS, 2care4 ApS, Strides Nordic ApS, Paranova Danmark A/S, Abacus Medicine A/S, Karo Healthcare AB, Orifarm Generics A/S, EQL Pharma AB</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>5579000</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>20900000</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, Teva Denmark A/S, Karo Healthcare AB, EQL Pharma AB, Orifarm Generics A/S, Recordati AB, Krka Sverige AB, Sandoz A/S, Recordati AB, Viatris ApS, Krka Sverige AB, Recordati AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB, Krka Sverige AB</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>43084000</v>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>91400000</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Krka Sverige AB, Sandoz A/S, STADA Nordic ApS, Sanofi A/S, Orifarm Generics A/S, Teva Denmark A/S, Sandoz A/S, Teva Denmark A/S, Orifarm Generics A/S, 2care4 Generics ApS, Viatris ApS, 2care4 ApS, Zentiva Denmark ApS, Orifarm A/S, Zentiva Denmark ApS, Krka Sverige AB, Zentiva Denmark ApS, Orifarm Generics A/S, Krka Sverige AB, Zentiva Denmark ApS, Orifarm Generics A/S, EQL Pharma AB, Orifarm Generics A/S, Teva Denmark A/S, EQL Pharma AB, Abacus Medicine A/S, Takeda Pharma A/S, Takeda Pharma A/S, Abacus Medicine A/S, Strides Nordic ApS, Omet Pharma AB, Orifarm Generics A/S, Strides Nordic ApS, Omet Pharma AB, STADA Nordic ApS, STADA Nordic ApS, STADA Nordic ApS, Sandoz A/S, Orifarm Generics A/S, Teva Denmark A/S, Sandoz A/S, Orifarm Generics A/S, Teva Denmark A/S</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>32792000</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>383000000</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>LEO Pharma A/S, Mundipharma A/S, Pharmanovia A/S, Pharmanovia A/S, Øresund Pharma ApS, Orifarm Generics A/S, Paranova Danmark A/S, 2care4 ApS, Abacus Medicine A/S, Abacus Medicine A/S, Orifarm A/S, CampusPharma AB, SERB SAS</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>6020000</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>12200001</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>2care4 Generics ApS, Haleon Denmark ApS, Haleon Denmark ApS, Haleon Denmark ApS, Teva Denmark A/S, EQL Pharma AB, EQL Pharma AB, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1860000</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>5040002</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Paranova Danmark A/S, Orifarm A/S, 2care4 Generics ApS, EQL Pharma AB, 2care4 Generics ApS, Viatris ApS</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>8465000</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>33399999</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Viatris ApS, EQL Pharma AB, Orifarm Generics A/S, Viatris ApS, Orion Pharma A/S, Orifarm Generics A/S, Orion Pharma A/S, Orion Pharma A/S, Orifarm Generics A/S, 2care4 ApS, Teva Denmark A/S, Krka Sverige AB, STADA Nordic ApS, Teva Denmark A/S, Pfizer ApS, Krka Sverige AB, Sandoz A/S, STADA Nordic ApS, Krka Sverige AB, Orifarm A/S, Sandoz A/S, Paranova Danmark A/S, 2care4 ApS, Orifarm A/S, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>38466000</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>178000002</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Panpharma Nordic AS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Panpharma Nordic AS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Panpharma Nordic AS, EQL Pharma AB, Sandoz A/S, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Navamedic AB, Navamedic AB, Panpharma Nordic AS, Abcur AB, Macure Pharma ApS, Grindeks Kalceks Danmark ApS, Hameln Pharma ApS, Pfizer ApS, Abcur AB, Panpharma Nordic AS, Sandoz A/S, Sandoz A/S, Macure Pharma ApS, Orifarm A/S, 2care4 ApS, Orifarm A/S, 2care4 ApS, Abacus Medicine A/S</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>10167000</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>37700001</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>FrostPharma AB, Orifarm Generics A/S, Grindeks Kalceks Danmark ApS, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, Unimedic Pharma AB, Orifarm Generics A/S, Abcur AB</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>325000000</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>650000000</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB, Norgine A/S, G.L. Pharma Nordic Aktiebolag, EQL Pharma AB, Corza Medical Gmbh, Abcur AB, Grindeks Kalceks Sverige AB, Pfizer Aktiebolag, Bayer Aktiebolag, CSL Behring Aktiebolag, Macure Pharma, Takeda Pharma AB, Sandoz A/S, Novo Nordisk Scandinavia AB, Ebb Medical, Orifarm AB, Unimedic Pharma AB, Fresenius Kabi AB, Roche Aktiebolag, FrostPharma AB, Baxter Medical AB, Orifarm Generics AB, Gentili Pharma AS, hameln pharma AB, Aguettant Nordic ApS, B.Braun Medical AB, XGX Pharma ApS, Accord Healthcare AB, Aspen Pharma Ireland Limited, Viatris AB</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>13690000</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>MSD Danmark ApS, EQL Pharma AB, Fresenius Kabi, Filial af Fresenius Kabi AB, Sverige, 2care4 ApS, Abcur AB, Abacus Medicine A/S, Orifarm A/S, 2care4 ApS</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Region Kalmar Län</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Orifarm Generics AB, B Braun Medical AB, SUN Pharmaceuticals GmbH, Baxter Medical AB, Aspen Pharma Ireland Limited, Grindeks Kalceks Sverige AB, AGUETTANT NORDIC ApS, EQL Pharma AB, Camurus AB, Viatris AB, Fresenius Kabi, Haleon Sweden AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-15Z</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>410000000</v>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Region Västernorrland</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-03-11Z</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Region Jönköpings Län</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12Z</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-24Z</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-15Z</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>268138000</v>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>447642000</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2024-07-17Z</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>1063000000</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>1063000000</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Zentiva Denmark ApS</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>244000000</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>840000000</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag, Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2345,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3019,6 +3019,38 @@
           <t>SEK</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>42538000</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Region Värmland</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Medovia AB</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
